--- a/templates/CAPITANIA CANA - template.xlsx
+++ b/templates/CAPITANIA CANA - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1316,8 +1316,8 @@
     <col width="17.28515625" customWidth="1" style="1" min="1" max="1"/>
     <col width="18.7109375" customWidth="1" style="1" min="2" max="6"/>
     <col width="21.5703125" customWidth="1" style="1" min="7" max="7"/>
-    <col width="17.28515625" customWidth="1" style="1" min="8" max="12"/>
-    <col width="17.28515625" customWidth="1" style="1" min="13" max="16384"/>
+    <col width="17.28515625" customWidth="1" style="1" min="8" max="13"/>
+    <col width="17.28515625" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1462,40 +1462,40 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="9">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>1.2362972</v>
+        <v>1.2423267</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>-0.0008644970218614212</v>
+        <v>0.0001926595503667361</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>-0.0004173049558622299</v>
+        <v>0.001228260330804476</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>2.071619351069553</v>
+        <v>0.1568556319331338</v>
       </c>
     </row>
     <row r="18" ht="15.95" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>1.2373669</v>
+        <v>1.2420874</v>
       </c>
       <c r="D18" s="31" t="n">
-        <v>0.0004112031265020022</v>
+        <v>0.0003008744849255507</v>
       </c>
       <c r="E18" s="31" t="n">
-        <v>0.001008317718015572</v>
+        <v>0.001228864396657148</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>0.4078110690262131</v>
+        <v>0.2448394515652116</v>
       </c>
       <c r="G18" s="4" t="n"/>
     </row>
@@ -1503,20 +1503,20 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>1.2368583</v>
+        <v>1.2417138</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>0.0003142009614791608</v>
+        <v>0.001431603030053186</v>
       </c>
       <c r="E19" s="31" t="n">
-        <v>-0.000369098634551146</v>
+        <v>0.003055672154189226</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>-0.851265575287903</v>
+        <v>0.4685067500093245</v>
       </c>
       <c r="G19" s="4" t="n"/>
     </row>
@@ -1524,20 +1524,20 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>1.2364698</v>
+        <v>1.2399387</v>
       </c>
       <c r="D20" s="31" t="n">
-        <v>0.0009007112194521216</v>
+        <v>-0.001398674726100002</v>
       </c>
       <c r="E20" s="31" t="n">
-        <v>0.002424076115274953</v>
+        <v>0.0001401648621799367</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>0.3715688685583858</v>
+        <v>-9.978782872874747</v>
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
@@ -1545,20 +1545,20 @@
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>1.2353571</v>
+        <v>1.2416754</v>
       </c>
       <c r="D21" s="31" t="n">
-        <v>0.002122343967199125</v>
+        <v>0.0005707645271177952</v>
       </c>
       <c r="E21" s="31" t="n">
-        <v>-0.001141971242602069</v>
+        <v>-7.902904525247667e-05</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>-1.858491604712569</v>
+        <v>-7.222212103086342</v>
       </c>
       <c r="G21" s="4" t="n"/>
     </row>
@@ -1600,18 +1600,18 @@
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="47" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="42" t="inlineStr"/>
       <c r="D24" s="42" t="n">
-        <v>-0.005086840028578177</v>
+        <v>0.001674662771537161</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>0.006369420073854881</v>
+        <v>0.007488477748118338</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>-0.7986347217792364</v>
+        <v>0.2236319353366524</v>
       </c>
       <c r="G24" s="14" t="n"/>
     </row>
@@ -1624,13 +1624,13 @@
       </c>
       <c r="C25" s="43" t="inlineStr"/>
       <c r="D25" s="43" t="n">
-        <v>-0.002949141661706678</v>
+        <v>0.002034514640737894</v>
       </c>
       <c r="E25" s="31" t="n">
-        <v>0.008564754015659926</v>
+        <v>0.02051942488737701</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>-0.3443346599697344</v>
+        <v>0.09915066586439622</v>
       </c>
       <c r="G25" s="41" t="n"/>
     </row>
@@ -1643,13 +1643,13 @@
       </c>
       <c r="C26" s="43" t="inlineStr"/>
       <c r="D26" s="43" t="n">
-        <v>0.02800934764705643</v>
+        <v>0.02737898288937624</v>
       </c>
       <c r="E26" s="31" t="n">
-        <v>0.03540704738942546</v>
+        <v>0.04413395526982056</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>0.7910670251318836</v>
+        <v>0.6203609606705335</v>
       </c>
       <c r="G26" s="15" t="n"/>
     </row>
@@ -1662,13 +1662,13 @@
       </c>
       <c r="C27" s="43" t="inlineStr"/>
       <c r="D27" s="43" t="n">
-        <v>0.05717506073661061</v>
+        <v>0.05843441123540227</v>
       </c>
       <c r="E27" s="31" t="n">
-        <v>0.06212331211768896</v>
+        <v>0.07820231730317562</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>0.9203479142949722</v>
+        <v>0.7472209680035835</v>
       </c>
       <c r="G27" s="15" t="n"/>
     </row>
@@ -1681,18 +1681,18 @@
       </c>
       <c r="C28" s="43" t="inlineStr"/>
       <c r="D28" s="43" t="n">
-        <v>0.1402833992973818</v>
+        <v>0.13710939877651</v>
       </c>
       <c r="E28" s="31" t="n">
-        <v>0.1176647437940919</v>
+        <v>0.1297857302122285</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>1.192229675380686</v>
+        <v>1.056428919822739</v>
       </c>
       <c r="G28" s="15" t="n"/>
     </row>
-    <row r="29" ht="15.95" customFormat="1" customHeight="1" s="30">
-      <c r="A29" s="54" t="n"/>
+    <row r="29" ht="15.95" customHeight="1">
+      <c r="A29" s="10" t="n"/>
       <c r="B29" s="48" t="inlineStr">
         <is>
           <t>Ano 2026</t>
@@ -1700,14 +1700,15 @@
       </c>
       <c r="C29" s="43" t="inlineStr"/>
       <c r="D29" s="43" t="n">
-        <v>0.02355964266485766</v>
+        <v>0.02855160808016999</v>
       </c>
       <c r="E29" s="31" t="n">
-        <v>0.03089355229913116</v>
+        <v>0.04642807189443898</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>0.7626071109187482</v>
-      </c>
+        <v>0.6149643290181477</v>
+      </c>
+      <c r="G29" s="15" t="n"/>
     </row>
     <row r="30" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="A30" s="54" t="n"/>
@@ -1727,14 +1728,14 @@
         <v>1.286165678329432</v>
       </c>
     </row>
-    <row r="31" ht="15.95" customHeight="1">
-      <c r="A31" s="16" t="n"/>
+    <row r="31" ht="15.95" customFormat="1" customHeight="1" s="30">
+      <c r="A31" s="54" t="n"/>
       <c r="B31" s="48" t="inlineStr">
         <is>
           <t>Ano 2024</t>
         </is>
       </c>
-      <c r="C31" s="48" t="inlineStr"/>
+      <c r="C31" s="43" t="inlineStr"/>
       <c r="D31" s="43" t="n">
         <v>0.0504408999999999</v>
       </c>
@@ -1744,7 +1745,6 @@
       <c r="F31" s="32" t="n">
         <v>1.834897004910543</v>
       </c>
-      <c r="G31" s="4" t="n"/>
     </row>
     <row r="32" ht="15.95" customHeight="1">
       <c r="A32" s="16" t="n"/>
@@ -1755,18 +1755,18 @@
       </c>
       <c r="C32" s="48" t="inlineStr"/>
       <c r="D32" s="43" t="n">
-        <v>0.2362972000000001</v>
+        <v>0.2423267</v>
       </c>
       <c r="E32" s="31" t="n">
-        <v>0.1826360927851411</v>
+        <v>0.2004572184644278</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>1.293814362739284</v>
+        <v>1.208869911776224</v>
       </c>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34" ht="26.1" customHeight="1">
+    <row r="33" ht="15.95" customHeight="1"/>
+    <row r="34">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="44" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       <c r="F34" s="44" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35" ht="15.95" customHeight="1">
+    <row r="35" ht="26.1" customHeight="1">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="33" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       <c r="C35" s="34" t="n"/>
       <c r="D35" s="34" t="n"/>
       <c r="E35" s="45" t="n">
-        <v>62781435.99</v>
+        <v>63087628.01</v>
       </c>
       <c r="F35" s="45" t="n"/>
       <c r="G35" s="4" t="n"/>
@@ -1804,7 +1804,7 @@
       <c r="C36" s="34" t="n"/>
       <c r="D36" s="34" t="n"/>
       <c r="E36" s="45" t="n">
-        <v>59217701.60162698</v>
+        <v>59520562.83829365</v>
       </c>
       <c r="F36" s="45" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C38" s="37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D38" s="38" t="n"/>
@@ -1861,7 +1861,7 @@
       <c r="F40" s="19" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="47.25" customHeight="1">
+    <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="10" t="n"/>
       <c r="B41" s="49" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       <c r="F41" s="49" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
-    <row r="42" ht="12.75" customHeight="1">
+    <row r="42" ht="47.25" customHeight="1">
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="50" t="n"/>
       <c r="C42" s="50" t="n"/>
@@ -1883,7 +1883,7 @@
       <c r="F42" s="50" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="20" t="n"/>
       <c r="C43" s="20" t="n"/>
@@ -1913,6 +1913,6 @@
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="87" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="84"/>
 </worksheet>
 </file>